--- a/2_cointegrated_pairs.xlsx
+++ b/2_cointegrated_pairs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,253 +483,1117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MDTUSDT</t>
+          <t>FOXYUSDT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAKEUSDT</t>
+          <t>1000000MOGUSDT</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.52</v>
+        <v>-5.62</v>
       </c>
       <c r="E2" t="n">
         <v>-3.37</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02315247491838156</v>
+        <v>0.00512037234376348</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>2.456204740582103</v>
+        <v>-2.508272933410532</v>
       </c>
       <c r="I2" t="n">
-        <v>2.456204740582103</v>
+        <v>2.508272933410532</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7399924154774947</v>
+        <v>0.6599697415672752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RADUSDT</t>
+          <t>ANKRUSDT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SLPUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.93</v>
+        <v>-4.34</v>
       </c>
       <c r="E3" t="n">
         <v>-3.37</v>
       </c>
       <c r="F3" t="n">
-        <v>431.6203056320805</v>
+        <v>0.0009419626058445459</v>
       </c>
       <c r="G3" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.802706882828792</v>
+        <v>-2.51893365322597</v>
       </c>
       <c r="I3" t="n">
-        <v>2.802706882828792</v>
+        <v>2.51893365322597</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4500000000000002</v>
+        <v>0.5845450549976816</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MDTUSDT</t>
+          <t>EIGENUSDT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RADUSDT</t>
+          <t>MOBILEUSDT</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.57</v>
+        <v>-4.68</v>
       </c>
       <c r="E4" t="n">
         <v>-3.37</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03741065653899991</v>
+        <v>3449.213622262337</v>
       </c>
       <c r="G4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>2.605594580902284</v>
+        <v>-3.451272840161125</v>
       </c>
       <c r="I4" t="n">
-        <v>2.605594580902284</v>
+        <v>3.451272840161125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3020912650892226</v>
+        <v>0.5454594144665544</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CTKUSDT</t>
+          <t>1000000BABYDOGEUSDT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BCHUSDT</t>
+          <t>HNTUSDT</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.12</v>
+        <v>-4.84</v>
       </c>
       <c r="E5" t="n">
         <v>-3.37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001680653672749637</v>
+        <v>0.0004299809101034289</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.31203658031444</v>
+        <v>-3.660247678022071</v>
       </c>
       <c r="I5" t="n">
-        <v>2.31203658031444</v>
+        <v>3.660247678022071</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2651451330339672</v>
+        <v>0.4892857142857144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTCUSDT</t>
+          <t>ARKUSDT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XVGUSDT</t>
+          <t>SHIB1000USDT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.51</v>
+        <v>-4.06</v>
       </c>
       <c r="E6" t="n">
         <v>-3.37</v>
       </c>
       <c r="F6" t="n">
-        <v>114.2351074441845</v>
+        <v>25.7469580008758</v>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>2.279652501055378</v>
+        <v>3.185639938701691</v>
       </c>
       <c r="I6" t="n">
-        <v>2.279652501055378</v>
+        <v>3.185639938701691</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2408448324051201</v>
+        <v>0.4277664047483836</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HFTUSDT</t>
+          <t>ENSUSDT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BALUSDT</t>
+          <t>FLRUSDT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.98</v>
+        <v>-4.41</v>
       </c>
       <c r="E7" t="n">
         <v>-3.37</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07588516995535464</v>
+        <v>1251.593436104739</v>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
-        <v>2.203009130559901</v>
+        <v>-2.23399003331698</v>
       </c>
       <c r="I7" t="n">
-        <v>2.203009130559901</v>
+        <v>2.23399003331698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1833333333333337</v>
+        <v>0.4218663548305704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DODOUSDT</t>
+          <t>MOBILEUSDT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NKNUSDT</t>
+          <t>TAIKOUSDT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.09</v>
+        <v>-4.32</v>
       </c>
       <c r="E8" t="n">
         <v>-3.37</v>
       </c>
       <c r="F8" t="n">
-        <v>1.627761738959612</v>
+        <v>0.0005839832812762483</v>
       </c>
       <c r="G8" t="n">
         <v>34</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.209465009284051</v>
+        <v>2.595508627372399</v>
       </c>
       <c r="I8" t="n">
-        <v>2.209465009284051</v>
+        <v>2.595508627372399</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00484434936578686</v>
+        <v>0.4107192431958152</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GUSDT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TAOUSDT</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6.052498220600618e-05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-2.142351736190777</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.142351736190777</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3948173296675532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MOBILEUSDT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OPUSDT</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0005100001160827527</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.280919772186125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.280919772186125</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3773188795478263</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MOBILEUSDT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SNXUSDT</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0004997412910769642</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.940152912012408</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.940152912012408</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3553055999282342</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LQTYUSDT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ENAUSDT</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.996930165271802</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.511541493104374</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.511541493104374</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3466488133609422</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ATHUSDT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVCUSDT</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3827240290695777</v>
+      </c>
+      <c r="G13" t="n">
+        <v>31</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2.561523112963567</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.561523112963567</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2828305407915044</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CELOUSDT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OSMOUSDT</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.367631818749924</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.548270539340149</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.548270539340149</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2789187570869152</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ETHWUSDT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7.344701899375981</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2.933706939535499</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.933706939535499</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2748315031798981</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1000000MOGUSDT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PIXELUSDT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F16" t="n">
+        <v>12.16311894267207</v>
+      </c>
+      <c r="G16" t="n">
+        <v>33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.21668958568257</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.21668958568257</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.2596168964296154</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10000000AIDOGEUSDT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ORDIUSDT</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.861601379057048e-05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>31</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.349222210093288</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.349222210093288</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2201653380983455</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BATUSDT</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F18" t="n">
+        <v>153.1356497197214</v>
+      </c>
+      <c r="G18" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.527090640962238</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.527090640962238</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.1940956234735949</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SUPERUSDT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SSVUSDT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.05930404074414549</v>
+      </c>
+      <c r="G19" t="n">
+        <v>29</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.400074306077236</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.400074306077236</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1566040053820119</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1000000MOGUSDT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ALTUSDT</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17.64200586565632</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.333900664755674</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.333900664755674</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1370714240773819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NTRNUSDT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SEIUSDT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8843734550947008</v>
+      </c>
+      <c r="G21" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-2.510056123200803</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.510056123200803</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.110496088597066</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TRUUSDT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AEROUSDT</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.06527117738868937</v>
+      </c>
+      <c r="G22" t="n">
+        <v>28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2.358769792674356</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.358769792674356</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1051263707156514</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BOBAUSDT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TAIKOUSDT</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1334415251887122</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.317977092868969</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.317977092868969</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.09308552318676587</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TAOUSDT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ETHBTCUSDT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13973.5173905197</v>
+      </c>
+      <c r="G24" t="n">
+        <v>28</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.278326319199762</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.278326319199762</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0813817398522238</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AEROUSDT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LISTAUSDT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.331804127146158</v>
+      </c>
+      <c r="G25" t="n">
+        <v>28</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.230176316815593</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.230176316815593</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.06716922535847392</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TAOUSDT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ETHWUSDT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F26" t="n">
+        <v>155.5063817719998</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.223244773467493</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.223244773467493</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.06512323043799771</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BANDUSDT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EGLDUSDT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.04195811699833024</v>
+      </c>
+      <c r="G27" t="n">
+        <v>28</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.193835413635667</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.193835413635667</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.05644242187797247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AEROUSDT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MOBILEUSDT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1393.425549630322</v>
+      </c>
+      <c r="G28" t="n">
+        <v>28</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-2.187867312257373</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.187867312257373</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.05468080769024274</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NULSUSDT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BOBAUSDT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.686129788403823</v>
+      </c>
+      <c r="G29" t="n">
+        <v>27</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2.312869207972957</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.312869207972957</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.05229210621107529</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1000000MOGUSDT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1000CATUSDT</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F30" t="n">
+        <v>59.58868714235672</v>
+      </c>
+      <c r="G30" t="n">
+        <v>27</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.263682459072619</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.263682459072619</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0377735735624385</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BAKEUSDT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STORJUSDT</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.524507978085782</v>
+      </c>
+      <c r="G31" t="n">
+        <v>27</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-2.254021096628568</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.254021096628568</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.03492181350083186</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FILUSDT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AVAXUSDT</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-3.92</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1374249769696807</v>
+      </c>
+      <c r="G32" t="n">
+        <v>27</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-2.135710898664372</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.135710898664372</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
